--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -63,9 +63,6 @@
     <t>PrefabPath</t>
   </si>
   <si>
-    <t>mob_slim_1</t>
-  </si>
-  <si>
     <t>mob_dog_1</t>
   </si>
   <si>
@@ -163,6 +160,10 @@
   </si>
   <si>
     <t>float[]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_slim_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -511,7 +512,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -520,7 +521,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -763,22 +764,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>34</v>
-      </c>
       <c r="G1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="12.75">
@@ -792,16 +793,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>7</v>
@@ -821,16 +822,16 @@
         <v>12</v>
       </c>
       <c r="D3" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="F3" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>30</v>
-      </c>
       <c r="G3" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>2</v>
@@ -841,13 +842,13 @@
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="19">
         <v>500</v>
@@ -862,10 +863,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -879,7 +880,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>9</v>
@@ -905,7 +906,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>10</v>
@@ -931,13 +932,13 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="D7" s="19">
         <v>1000</v>
@@ -949,13 +950,13 @@
         <v>0.5</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -19,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
-  <si>
-    <t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -36,24 +33,12 @@
     <t>Id</t>
   </si>
   <si>
-    <t>도그는 도그다</t>
-  </si>
-  <si>
     <t>(name)</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>슬라이무</t>
-  </si>
-  <si>
-    <t>도그</t>
-  </si>
-  <si>
-    <t>피그미</t>
-  </si>
-  <si>
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
@@ -63,45 +48,10 @@
     <t>PrefabPath</t>
   </si>
   <si>
-    <t>mob_dog_1</t>
-  </si>
-  <si>
-    <t>mob_pigme_1</t>
-  </si>
-  <si>
     <t>몬스터 표기용 Icon</t>
   </si>
   <si>
     <t>몬스터를 우선 프리팹으로 구현</t>
-  </si>
-  <si>
-    <t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</t>
-  </si>
-  <si>
-    <t>mob_bear_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰저씨</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰 아저씨다. 반갑곰~</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Icon_Bear</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Slime</t>
-  </si>
-  <si>
-    <t>2DObject/Monster_Bear</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2DObject/Monster_Slime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
@@ -155,16 +105,81 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1.5,5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>float[]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>mob_slim_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>2DObject/Monster_Bandit</t>
+  </si>
+  <si>
+    <t>약탈자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모험가들을 약탈한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_bandit_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_goblin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>산에 서식하는 고블린이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/Monster_Goblin</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2DObject/Monster_Mushroom </t>
+  </si>
+  <si>
+    <t>mob_mushroom _1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴물버섯</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>산에 서식 하는 괴물버섯이다.독성이 매우 강하다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/Monster_Skeleton</t>
+  </si>
+  <si>
+    <t>스켈레톤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_skeleton_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스켈레톤이다.덜그럭..덜그럭..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Bandit</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Skul</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Goblin</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Mushroom</t>
   </si>
 </sst>
 </file>
@@ -757,104 +772,104 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>2</v>
-      </c>
       <c r="I3" s="14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D4" s="19">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E4" s="19">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F4" s="19">
         <v>1</v>
@@ -863,10 +878,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -880,20 +895,32 @@
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="D5" s="19">
+        <v>700</v>
+      </c>
+      <c r="E5" s="19">
+        <v>50</v>
+      </c>
+      <c r="F5" s="19">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -906,20 +933,32 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="D6" s="19">
+        <v>600</v>
+      </c>
+      <c r="E6" s="19">
+        <v>45</v>
+      </c>
+      <c r="F6" s="19">
+        <v>1</v>
+      </c>
+      <c r="G6" s="19">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -932,31 +971,31 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D7" s="19">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E7" s="19">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F7" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="G7" s="21">
+        <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
